--- a/project/outputs_xlsx_solution/test_new4.4-wide-NC-1.xlsx
+++ b/project/outputs_xlsx_solution/test_new4.4-wide-NC-1.xlsx
@@ -1111,7 +1111,7 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O16" t="s">
         <v>14</v>
@@ -1123,9 +1123,6 @@
         <v>14</v>
       </c>
       <c r="R16" t="s">
-        <v>14</v>
-      </c>
-      <c r="S16" t="s">
         <v>19</v>
       </c>
       <c r="W16" t="s">
@@ -1151,6 +1148,9 @@
       <c r="N17" t="s">
         <v>21</v>
       </c>
+      <c r="R17" t="s">
+        <v>14</v>
+      </c>
       <c r="S17" t="s">
         <v>14</v>
       </c>
@@ -1158,9 +1158,6 @@
         <v>14</v>
       </c>
       <c r="U17" t="s">
-        <v>14</v>
-      </c>
-      <c r="V17" t="s">
         <v>19</v>
       </c>
       <c r="X17" t="s">
@@ -1184,12 +1181,9 @@
         <v>9</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O18" t="s">
-        <v>14</v>
-      </c>
-      <c r="P18" t="s">
         <v>19</v>
       </c>
       <c r="Y18" t="s">
@@ -1215,10 +1209,10 @@
       <c r="N19" t="s">
         <v>21</v>
       </c>
+      <c r="O19" t="s">
+        <v>14</v>
+      </c>
       <c r="P19" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q19" t="s">
         <v>19</v>
       </c>
       <c r="Z19" t="s">
@@ -1242,12 +1236,9 @@
         <v>9</v>
       </c>
       <c r="O20" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P20" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" t="s">
         <v>19</v>
       </c>
       <c r="AA20" t="s">
@@ -1273,13 +1264,10 @@
       <c r="O21" t="s">
         <v>21</v>
       </c>
+      <c r="P21" t="s">
+        <v>14</v>
+      </c>
       <c r="Q21" t="s">
-        <v>15</v>
-      </c>
-      <c r="R21" t="s">
-        <v>14</v>
-      </c>
-      <c r="S21" t="s">
         <v>19</v>
       </c>
       <c r="AB21" t="s">
@@ -1305,10 +1293,10 @@
       <c r="O22" t="s">
         <v>21</v>
       </c>
-      <c r="S22" t="s">
-        <v>14</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="Q22" t="s">
+        <v>14</v>
+      </c>
+      <c r="R22" t="s">
         <v>19</v>
       </c>
       <c r="AC22" t="s">
@@ -1332,13 +1320,13 @@
         <v>9</v>
       </c>
       <c r="P23" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q23" t="s">
         <v>15</v>
       </c>
       <c r="R23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S23" t="s">
         <v>14</v>
@@ -1350,9 +1338,6 @@
         <v>14</v>
       </c>
       <c r="V23" t="s">
-        <v>14</v>
-      </c>
-      <c r="W23" t="s">
         <v>19</v>
       </c>
       <c r="AD23" t="s">
@@ -1378,6 +1363,9 @@
       <c r="P24" t="s">
         <v>21</v>
       </c>
+      <c r="V24" t="s">
+        <v>14</v>
+      </c>
       <c r="W24" t="s">
         <v>14</v>
       </c>
@@ -1385,9 +1373,6 @@
         <v>14</v>
       </c>
       <c r="Y24" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z24" t="s">
         <v>19</v>
       </c>
       <c r="AE24" t="s">
@@ -1411,7 +1396,7 @@
         <v>9</v>
       </c>
       <c r="P25" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="s">
         <v>14</v>
@@ -1475,12 +1460,9 @@
         <v>24</v>
       </c>
       <c r="R27" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="S27" t="s">
-        <v>14</v>
-      </c>
-      <c r="T27" t="s">
         <v>19</v>
       </c>
       <c r="AH27" t="s">
@@ -1507,12 +1489,9 @@
         <v>24</v>
       </c>
       <c r="S28" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T28" t="s">
-        <v>14</v>
-      </c>
-      <c r="U28" t="s">
         <v>19</v>
       </c>
       <c r="AI28" t="s">
@@ -1539,12 +1518,9 @@
         <v>24</v>
       </c>
       <c r="T29" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="U29" t="s">
-        <v>14</v>
-      </c>
-      <c r="V29" t="s">
         <v>19</v>
       </c>
       <c r="AJ29" t="s">
@@ -1571,10 +1547,10 @@
         <v>24</v>
       </c>
       <c r="U30" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="V30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W30" t="s">
         <v>14</v>
@@ -1586,9 +1562,6 @@
         <v>14</v>
       </c>
       <c r="Z30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA30" t="s">
         <v>19</v>
       </c>
       <c r="AK30" t="s">
@@ -1617,6 +1590,9 @@
       <c r="V31" t="s">
         <v>21</v>
       </c>
+      <c r="Z31" t="s">
+        <v>14</v>
+      </c>
       <c r="AA31" t="s">
         <v>14</v>
       </c>
@@ -1624,9 +1600,6 @@
         <v>14</v>
       </c>
       <c r="AC31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD31" t="s">
         <v>19</v>
       </c>
       <c r="AL31" t="s">
@@ -1653,12 +1626,9 @@
         <v>24</v>
       </c>
       <c r="W32" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="X32" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y32" t="s">
         <v>19</v>
       </c>
       <c r="AM32" t="s">
@@ -1685,12 +1655,9 @@
         <v>24</v>
       </c>
       <c r="X33" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y33" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z33" t="s">
         <v>19</v>
       </c>
       <c r="AN33" t="s">
@@ -1717,12 +1684,9 @@
         <v>24</v>
       </c>
       <c r="Y34" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Z34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA34" t="s">
         <v>19</v>
       </c>
       <c r="AO34" t="s">
@@ -1749,12 +1713,9 @@
         <v>24</v>
       </c>
       <c r="Z35" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB35" t="s">
         <v>19</v>
       </c>
       <c r="AP35" t="s">
@@ -1781,12 +1742,9 @@
         <v>24</v>
       </c>
       <c r="AA36" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AB36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC36" t="s">
         <v>19</v>
       </c>
       <c r="AQ36" t="s">
@@ -1813,7 +1771,7 @@
         <v>24</v>
       </c>
       <c r="AB37" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AC37" t="s">
         <v>14</v>
@@ -1825,9 +1783,6 @@
         <v>14</v>
       </c>
       <c r="AF37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG37" t="s">
         <v>19</v>
       </c>
       <c r="AR37" t="s">
@@ -1856,6 +1811,9 @@
       <c r="AC38" t="s">
         <v>21</v>
       </c>
+      <c r="AF38" t="s">
+        <v>14</v>
+      </c>
       <c r="AG38" t="s">
         <v>14</v>
       </c>
@@ -1863,9 +1821,6 @@
         <v>14</v>
       </c>
       <c r="AI38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ38" t="s">
         <v>19</v>
       </c>
       <c r="AS38" t="s">
@@ -1892,12 +1847,9 @@
         <v>24</v>
       </c>
       <c r="AD39" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF39" t="s">
         <v>19</v>
       </c>
       <c r="AT39" t="s">
@@ -1924,12 +1876,9 @@
         <v>24</v>
       </c>
       <c r="AE40" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AF40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG40" t="s">
         <v>19</v>
       </c>
       <c r="AU40" t="s">
@@ -1956,12 +1905,9 @@
         <v>24</v>
       </c>
       <c r="AF41" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AG41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH41" t="s">
         <v>19</v>
       </c>
       <c r="AV41" t="s">
@@ -1988,12 +1934,9 @@
         <v>24</v>
       </c>
       <c r="AG42" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AH42" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI42" t="s">
         <v>19</v>
       </c>
       <c r="AW42" t="s">
@@ -2020,12 +1963,9 @@
         <v>24</v>
       </c>
       <c r="AH43" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AI43" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ43" t="s">
         <v>19</v>
       </c>
       <c r="AX43" t="s">
@@ -2042,19 +1982,16 @@
       <c r="C44" t="s">
         <v>25</v>
       </c>
+      <c r="AI44" t="s">
+        <v>5</v>
+      </c>
       <c r="AJ44" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AK44" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AL44" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN44" t="s">
         <v>19</v>
       </c>
       <c r="AY44" t="s">
